--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487970_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487970_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.063</v>
+        <v>6.7981</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6398</v>
+        <v>7.2345</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5767</v>
+        <v>-0.4363</v>
       </c>
       <c r="G2" t="n">
         <v>4.2438</v>
@@ -610,13 +610,13 @@
         <v>2.9733</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2074</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2458</v>
+        <v>0.3489</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0384</v>
+        <v>0.1788</v>
       </c>
       <c r="V2" t="n">
         <v>3.0178</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3599</v>
+        <v>3.2639</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3165</v>
+        <v>0.3436</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0434</v>
+        <v>2.9203</v>
       </c>
       <c r="G3" t="n">
         <v>1.2699</v>
@@ -688,13 +688,13 @@
         <v>3.1716</v>
       </c>
       <c r="S3" t="n">
-        <v>4.9335</v>
+        <v>2.8375</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4194</v>
+        <v>1.4465</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5142</v>
+        <v>1.391</v>
       </c>
       <c r="V3" t="n">
         <v>0.9405</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8292</v>
+        <v>3.081</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1742</v>
+        <v>2.0328</v>
       </c>
       <c r="F4" t="n">
-        <v>0.655</v>
+        <v>1.0481</v>
       </c>
       <c r="G4" t="n">
         <v>0.4237</v>
@@ -766,13 +766,13 @@
         <v>1.5858</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7247</v>
+        <v>0.9765</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9435</v>
+        <v>0.8022</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2188</v>
+        <v>0.1743</v>
       </c>
       <c r="V4" t="n">
         <v>2.0772</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6866</v>
+        <v>2.0485</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2955</v>
+        <v>0.394</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3911</v>
+        <v>1.6545</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.6247</v>
+        <v>0.0404</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4011</v>
+        <v>-1.5133</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.2235</v>
+        <v>1.5537</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9149</v>
+        <v>0.2129</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7938</v>
+        <v>-0.2485</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.7087</v>
+        <v>0.4614</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7098</v>
+        <v>-0.1725</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.195</v>
+        <v>-1.2648</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5148</v>
+        <v>1.0923</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R6" t="n">
         <v>2.9733</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9147999999999999</v>
+        <v>1.138</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1837</v>
+        <v>0.4737</v>
       </c>
       <c r="U6" t="n">
-        <v>0.731</v>
+        <v>0.6643</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4142</v>
+        <v>0.8701</v>
       </c>
       <c r="W6" t="n">
-        <v>3.0178</v>
+        <v>2.6808</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6036</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0545</v>
+        <v>1.6491</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.263</v>
+        <v>0.4827</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3175</v>
+        <v>1.1665</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0404</v>
+        <v>-3.6247</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5133</v>
+        <v>-0.4011</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5537</v>
+        <v>-3.2235</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2129</v>
+        <v>-1.9149</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2485</v>
+        <v>0.7938</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4614</v>
+        <v>-2.7087</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1725</v>
+        <v>-1.7098</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2648</v>
+        <v>-1.195</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0923</v>
+        <v>-0.5148</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
         <v>2.9733</v>
       </c>
       <c r="S7" t="n">
-        <v>0.144</v>
+        <v>0.8774</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1834</v>
+        <v>0.3709</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3274</v>
+        <v>0.5064</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8701</v>
+        <v>2.4142</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6808</v>
+        <v>3.0178</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8107</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="8">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4156</v>
+        <v>-0.5797</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1036</v>
+        <v>-2.3239</v>
       </c>
       <c r="F10" t="n">
-        <v>1.688</v>
+        <v>1.7441</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6756</v>
@@ -1234,13 +1234,13 @@
         <v>2.7751</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8656</v>
+        <v>1.7014</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3731</v>
+        <v>1.1528</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4925</v>
+        <v>0.5486</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4074</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3896</v>
+        <v>-0.6422</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3197</v>
+        <v>1.0952</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7093</v>
+        <v>-1.7374</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3111</v>
@@ -1312,13 +1312,13 @@
         <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.25</v>
+        <v>0.4974</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5505</v>
+        <v>0.2249</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3005</v>
+        <v>0.2724</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8107</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7344</v>
+        <v>-1.6398</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4582</v>
+        <v>-0.5601</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2762</v>
+        <v>-1.0797</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3119</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0965</v>
+        <v>-0.0018</v>
       </c>
       <c r="T12" t="n">
-        <v>0.18</v>
+        <v>0.0781</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2764</v>
+        <v>-0.0799</v>
       </c>
       <c r="V12" t="n">
         <v>0.674</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8426</v>
+        <v>-2.12</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0731</v>
+        <v>-2.6033</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2306</v>
+        <v>0.4833</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7012</v>
@@ -1468,13 +1468,13 @@
         <v>1.3876</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9254</v>
+        <v>-0.2028</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6864</v>
+        <v>-0.2165</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.239</v>
+        <v>0.0137</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6036</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.5323</v>
+        <v>15.7802</v>
       </c>
       <c r="E14" t="n">
-        <v>8.769099999999998</v>
+        <v>10.0168</v>
       </c>
       <c r="F14" t="n">
-        <v>5.7634</v>
+        <v>5.763399999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-1.725399999999999</v>
@@ -1546,13 +1546,13 @@
         <v>20.81329999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>7.103300000000001</v>
+        <v>8.3513</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4336</v>
+        <v>4.6815</v>
       </c>
       <c r="U14" t="n">
-        <v>3.669800000000001</v>
+        <v>3.6696</v>
       </c>
       <c r="V14" t="n">
         <v>7.172100000000002</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2508</v>
+        <v>5.0235</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7434</v>
+        <v>3.1322</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5074</v>
+        <v>1.8913</v>
       </c>
       <c r="G15" t="n">
         <v>1.9858</v>
@@ -1624,13 +1624,13 @@
         <v>2.7751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3729</v>
+        <v>-0.6002</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1727</v>
+        <v>-0.4385</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5456</v>
+        <v>-0.1617</v>
       </c>
       <c r="V15" t="n">
         <v>2.0521</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2014</v>
+        <v>1.3616</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4561</v>
+        <v>3.3355</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2547</v>
+        <v>-1.9739</v>
       </c>
       <c r="G16" t="n">
         <v>1.3821</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6388</v>
+        <v>-0.201</v>
       </c>
       <c r="T16" t="n">
-        <v>1.351</v>
+        <v>0.2305</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.4314</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2071</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1765</v>
+        <v>-0.419</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0602</v>
+        <v>1.5696</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2367</v>
+        <v>-1.9886</v>
       </c>
       <c r="G17" t="n">
         <v>3.1497</v>
@@ -1780,13 +1780,13 @@
         <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6688</v>
+        <v>-0.9113</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9984</v>
+        <v>-0.489</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6704</v>
+        <v>-0.4223</v>
       </c>
       <c r="V17" t="n">
         <v>-3.4503</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3572</v>
+        <v>-0.855</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0001</v>
+        <v>1.3057</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3573</v>
+        <v>-2.1607</v>
       </c>
       <c r="G18" t="n">
         <v>1.4117</v>
@@ -1858,13 +1858,13 @@
         <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5884</v>
+        <v>-0.0863</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.312</v>
+        <v>-0.0064</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2764</v>
+        <v>-0.0799</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3464</v>
+        <v>-2.3276</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2792</v>
+        <v>-1.8306</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0672</v>
+        <v>-0.497</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3678</v>
+        <v>-1.3477</v>
       </c>
       <c r="H19" t="n">
-        <v>1.345</v>
+        <v>1.2293</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0228</v>
+        <v>-2.5771</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0045</v>
+        <v>-0.3246</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0045</v>
+        <v>1.7491</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-2.0737</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6367</v>
+        <v>-1.0232</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6595</v>
+        <v>-0.5198</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0228</v>
+        <v>-0.5034</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.9645</v>
+        <v>-1.1893</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9822</v>
+        <v>2.9733</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1627</v>
+        <v>-1.5317</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3192</v>
+        <v>-0.9203</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1565</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5692</v>
+        <v>-1.2323</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5692</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6659</v>
+        <v>-2.6435</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7288</v>
+        <v>-2.4829</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9371</v>
+        <v>-0.1605</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3477</v>
+        <v>1.3678</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2293</v>
+        <v>1.345</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.5771</v>
+        <v>0.0228</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3246</v>
+        <v>2.0045</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7491</v>
+        <v>2.0045</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.0737</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0232</v>
+        <v>-0.6367</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5198</v>
+        <v>-0.6595</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5034</v>
+        <v>0.0228</v>
       </c>
       <c r="P20" t="n">
-        <v>1.784</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1893</v>
+        <v>-3.9645</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9733</v>
+        <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8699</v>
+        <v>-0.4598</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8184</v>
+        <v>-0.523</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0515</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2323</v>
+        <v>-1.5692</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8358</v>
+        <v>-1.5692</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4195</v>
+        <v>-3.6677</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5711</v>
+        <v>-4.047</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8484</v>
+        <v>0.3793</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3471</v>
+        <v>-2.3045</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0104</v>
+        <v>-1.3459</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3367</v>
+        <v>-0.9586</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1085</v>
+        <v>-1.0136</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0605</v>
+        <v>0.2565</v>
       </c>
       <c r="L21" t="n">
-        <v>0.048</v>
+        <v>-1.2701</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4556</v>
+        <v>-1.2909</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0709</v>
+        <v>-1.6024</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3847</v>
+        <v>0.3116</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1893</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1805</v>
+        <v>-5.352</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9911</v>
+        <v>3.3698</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.9251</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4992</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4267</v>
+        <v>-0.226</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8107</v>
+        <v>1.5441</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.0178</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8107</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4945</v>
+        <v>-4.5913</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6582</v>
+        <v>-2.2655</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1638</v>
+        <v>-2.3257</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3045</v>
+        <v>-1.3471</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3459</v>
+        <v>-1.0104</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9586</v>
+        <v>-0.3367</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0136</v>
+        <v>0.1085</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2565</v>
+        <v>0.0605</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2701</v>
+        <v>0.048</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2909</v>
+        <v>-1.4556</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6024</v>
+        <v>-1.0709</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3116</v>
+        <v>-0.3847</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9822</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.352</v>
+        <v>-2.1805</v>
       </c>
       <c r="R22" t="n">
-        <v>3.3698</v>
+        <v>0.9911</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7518</v>
+        <v>-0.2442</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3103</v>
+        <v>-0.1936</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4415</v>
+        <v>-0.0506</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5441</v>
+        <v>-1.8107</v>
       </c>
       <c r="W22" t="n">
-        <v>3.0178</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4737</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5246</v>
+        <v>-5.0551</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7858</v>
+        <v>-4.4802</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7387</v>
+        <v>-0.5748</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5725</v>
@@ -2248,13 +2248,13 @@
         <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2551</v>
+        <v>-0.7856</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.6304</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3191</v>
+        <v>-0.1552</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4988</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.5324</v>
+        <v>-13.1741</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.763300000000001</v>
+        <v>-5.763199999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.7689</v>
+        <v>-7.410600000000001</v>
       </c>
       <c r="G24" t="n">
         <v>1.7253</v>
@@ -2326,13 +2326,13 @@
         <v>18.8311</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.103199999999999</v>
+        <v>-5.7452</v>
       </c>
       <c r="T24" t="n">
         <v>-3.6698</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.4335</v>
+        <v>-2.0753</v>
       </c>
       <c r="V24" t="n">
         <v>-7.1722</v>
